--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0002T0006Z000C1N6_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0002T0006Z000C1N6_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>16.17470178327184</v>
+        <v>2.628389039781673</v>
       </c>
       <c r="D2" t="n">
-        <v>12.45336719339903</v>
+        <v>2.023672168927342</v>
       </c>
       <c r="E2" t="n">
-        <v>14.89359765714766</v>
+        <v>2.420209619286495</v>
       </c>
       <c r="F2" t="n">
-        <v>10.97892500840478</v>
+        <v>1.784075313865776</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>42.23388082635446</v>
+        <v>6.8630056342826</v>
       </c>
       <c r="D3" t="n">
-        <v>18.80761037670746</v>
+        <v>3.056236686214962</v>
       </c>
       <c r="E3" t="n">
-        <v>14.89359765714766</v>
+        <v>2.420209619286495</v>
       </c>
       <c r="F3" t="n">
-        <v>10.97892500840478</v>
+        <v>1.784075313865776</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>41.5283593249714</v>
+        <v>6.748358390307852</v>
       </c>
       <c r="D4" t="n">
-        <v>16.54963280380158</v>
+        <v>2.689315330617756</v>
       </c>
       <c r="E4" t="n">
-        <v>14.89359765714766</v>
+        <v>2.420209619286495</v>
       </c>
       <c r="F4" t="n">
-        <v>10.97892500840478</v>
+        <v>1.784075313865776</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>26.23317107501767</v>
+        <v>4.262890299690371</v>
       </c>
       <c r="D5" t="n">
-        <v>29.87351133048941</v>
+        <v>4.854445591204529</v>
       </c>
       <c r="E5" t="n">
-        <v>14.89359765714766</v>
+        <v>2.420209619286495</v>
       </c>
       <c r="F5" t="n">
-        <v>10.97892500840478</v>
+        <v>1.784075313865776</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>19.85054488304013</v>
+        <v>3.225713543494021</v>
       </c>
       <c r="D6" t="n">
-        <v>16.65544014816414</v>
+        <v>2.706509024076672</v>
       </c>
       <c r="E6" t="n">
-        <v>14.89359765714766</v>
+        <v>2.420209619286495</v>
       </c>
       <c r="F6" t="n">
-        <v>10.97892500840478</v>
+        <v>1.784075313865776</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>16.730424288982</v>
+        <v>2.718693946959575</v>
       </c>
       <c r="D7" t="n">
-        <v>13.0097331313374</v>
+        <v>2.114081633842327</v>
       </c>
       <c r="E7" t="n">
-        <v>14.89359765714766</v>
+        <v>2.420209619286495</v>
       </c>
       <c r="F7" t="n">
-        <v>10.97892500840478</v>
+        <v>1.784075313865776</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>28.95436842600351</v>
+        <v>4.705084869225571</v>
       </c>
       <c r="D8" t="n">
-        <v>11.43697978185455</v>
+        <v>1.858509214551365</v>
       </c>
       <c r="E8" t="n">
-        <v>14.89359765714766</v>
+        <v>2.420209619286495</v>
       </c>
       <c r="F8" t="n">
-        <v>10.97892500840478</v>
+        <v>1.784075313865776</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>6.314654788234661</v>
+        <v>1.026131403088132</v>
       </c>
       <c r="D9" t="n">
-        <v>6.632291322432381</v>
+        <v>1.077747339895262</v>
       </c>
       <c r="E9" t="n">
-        <v>14.89359765714766</v>
+        <v>2.420209619286495</v>
       </c>
       <c r="F9" t="n">
-        <v>10.97892500840478</v>
+        <v>1.784075313865776</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>46.70837158693463</v>
+        <v>7.590110382876878</v>
       </c>
       <c r="D10" t="n">
-        <v>14.24811381273745</v>
+        <v>2.315318494569836</v>
       </c>
       <c r="E10" t="n">
-        <v>14.89359765714766</v>
+        <v>2.420209619286495</v>
       </c>
       <c r="F10" t="n">
-        <v>10.97892500840478</v>
+        <v>1.784075313865776</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>22.80513167838071</v>
+        <v>3.705833897736865</v>
       </c>
       <c r="D11" t="n">
-        <v>14.73711498572753</v>
+        <v>2.394781185180723</v>
       </c>
       <c r="E11" t="n">
-        <v>14.89359765714766</v>
+        <v>2.420209619286495</v>
       </c>
       <c r="F11" t="n">
-        <v>10.97892500840478</v>
+        <v>1.784075313865776</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>49.04108758889012</v>
+        <v>7.969176733194645</v>
       </c>
       <c r="D12" t="n">
-        <v>14.29403415047415</v>
+        <v>2.32278054945205</v>
       </c>
       <c r="E12" t="n">
-        <v>14.89359765714766</v>
+        <v>2.420209619286495</v>
       </c>
       <c r="F12" t="n">
-        <v>10.97892500840478</v>
+        <v>1.784075313865776</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>51.57027613880288</v>
+        <v>8.380169872555468</v>
       </c>
       <c r="D13" t="n">
-        <v>42.71975045934947</v>
+        <v>6.941959449644289</v>
       </c>
       <c r="E13" t="n">
-        <v>14.89359765714766</v>
+        <v>2.420209619286495</v>
       </c>
       <c r="F13" t="n">
-        <v>10.97892500840478</v>
+        <v>1.784075313865776</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>32.69704698264669</v>
+        <v>5.313270134680088</v>
       </c>
       <c r="D14" t="n">
-        <v>21.19746100878897</v>
+        <v>3.444587413928207</v>
       </c>
       <c r="E14" t="n">
-        <v>14.89359765714766</v>
+        <v>2.420209619286495</v>
       </c>
       <c r="F14" t="n">
-        <v>10.97892500840478</v>
+        <v>1.784075313865776</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>55.14077917046521</v>
+        <v>8.960376615200596</v>
       </c>
       <c r="D15" t="n">
-        <v>14.13455573915203</v>
+        <v>2.296865307612206</v>
       </c>
       <c r="E15" t="n">
-        <v>14.89359765714766</v>
+        <v>2.420209619286495</v>
       </c>
       <c r="F15" t="n">
-        <v>10.97892500840478</v>
+        <v>1.784075313865776</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>47.35942117085165</v>
+        <v>7.695905940263394</v>
       </c>
       <c r="D16" t="n">
-        <v>11.05917585781911</v>
+        <v>1.797116076895606</v>
       </c>
       <c r="E16" t="n">
-        <v>14.89359765714766</v>
+        <v>2.420209619286495</v>
       </c>
       <c r="F16" t="n">
-        <v>10.97892500840478</v>
+        <v>1.784075313865776</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>44.80215717079248</v>
+        <v>7.280350540253779</v>
       </c>
       <c r="D17" t="n">
-        <v>38.33169758926918</v>
+        <v>6.228900858256242</v>
       </c>
       <c r="E17" t="n">
-        <v>14.89359765714766</v>
+        <v>2.420209619286495</v>
       </c>
       <c r="F17" t="n">
-        <v>10.97892500840478</v>
+        <v>1.784075313865776</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>47.891842767394</v>
+        <v>7.782424449701526</v>
       </c>
       <c r="D18" t="n">
-        <v>27.24166165473963</v>
+        <v>4.426770018895191</v>
       </c>
       <c r="E18" t="n">
-        <v>14.89359765714766</v>
+        <v>2.420209619286495</v>
       </c>
       <c r="F18" t="n">
-        <v>10.97892500840478</v>
+        <v>1.784075313865776</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>55.38522346668351</v>
+        <v>9.000098813336072</v>
       </c>
       <c r="D19" t="n">
-        <v>23.46419132718722</v>
+        <v>3.812931090667923</v>
       </c>
       <c r="E19" t="n">
-        <v>14.89359765714766</v>
+        <v>2.420209619286495</v>
       </c>
       <c r="F19" t="n">
-        <v>10.97892500840478</v>
+        <v>1.784075313865776</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>54.69406865428683</v>
+        <v>8.88778615632161</v>
       </c>
       <c r="D20" t="n">
-        <v>35.95920815939142</v>
+        <v>5.843371325901106</v>
       </c>
       <c r="E20" t="n">
-        <v>14.89359765714766</v>
+        <v>2.420209619286495</v>
       </c>
       <c r="F20" t="n">
-        <v>10.97892500840478</v>
+        <v>1.784075313865776</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>51.28919606026371</v>
+        <v>8.334494359792854</v>
       </c>
       <c r="D21" t="n">
-        <v>44.22695561981254</v>
+        <v>7.186880288219538</v>
       </c>
       <c r="E21" t="n">
-        <v>14.89359765714766</v>
+        <v>2.420209619286495</v>
       </c>
       <c r="F21" t="n">
-        <v>10.97892500840478</v>
+        <v>1.784075313865776</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
